--- a/FIG.xlsx
+++ b/FIG.xlsx
@@ -640,7 +640,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -657,11 +657,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -689,6 +689,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -709,10 +713,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -723,10 +723,6 @@
     </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -769,10 +765,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,10 +774,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1011,7 +999,7 @@
       <sheetData sheetId="2">
         <row r="6">
           <cell r="L6">
-            <v>2.72916666666667</v>
+            <v>2.71416666666667</v>
           </cell>
         </row>
       </sheetData>
@@ -1372,184 +1360,184 @@
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
       <c r="D1" s="11"/>
-      <c r="AF1" s="0"/>
-    </row>
-    <row r="2" s="14" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="AF1" s="12"/>
+    </row>
+    <row r="2" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="14" t="n">
+      <c r="R2" s="15" t="n">
         <v>2023</v>
       </c>
-      <c r="S2" s="14" t="n">
+      <c r="S2" s="15" t="n">
         <f aca="false">+R2+1</f>
         <v>2024</v>
       </c>
-      <c r="T2" s="14" t="n">
+      <c r="T2" s="15" t="n">
         <f aca="false">+S2+1</f>
         <v>2025</v>
       </c>
-      <c r="U2" s="14" t="n">
+      <c r="U2" s="15" t="n">
         <f aca="false">+T2+1</f>
         <v>2026</v>
       </c>
-      <c r="V2" s="14" t="n">
+      <c r="V2" s="15" t="n">
         <f aca="false">+U2+1</f>
         <v>2027</v>
       </c>
-      <c r="W2" s="14" t="n">
+      <c r="W2" s="15" t="n">
         <f aca="false">+V2+1</f>
         <v>2028</v>
       </c>
-      <c r="X2" s="14" t="n">
+      <c r="X2" s="15" t="n">
         <f aca="false">+W2+1</f>
         <v>2029</v>
       </c>
-      <c r="Y2" s="14" t="n">
+      <c r="Y2" s="15" t="n">
         <f aca="false">+X2+1</f>
         <v>2030</v>
       </c>
-      <c r="Z2" s="14" t="n">
+      <c r="Z2" s="15" t="n">
         <f aca="false">+Y2+1</f>
         <v>2031</v>
       </c>
-      <c r="AA2" s="14" t="n">
+      <c r="AA2" s="15" t="n">
         <f aca="false">+Z2+1</f>
         <v>2032</v>
       </c>
-      <c r="AB2" s="14" t="n">
+      <c r="AB2" s="15" t="n">
         <f aca="false">+AA2+1</f>
         <v>2033</v>
       </c>
-      <c r="AC2" s="14" t="n">
+      <c r="AC2" s="15" t="n">
         <f aca="false">+AB2+1</f>
         <v>2034</v>
       </c>
-      <c r="AD2" s="14" t="n">
+      <c r="AD2" s="15" t="n">
         <f aca="false">+AC2+1</f>
         <v>2035</v>
       </c>
-      <c r="AE2" s="14" t="n">
+      <c r="AE2" s="15" t="n">
         <f aca="false">+AD2+1</f>
         <v>2036</v>
       </c>
-      <c r="AF2" s="0"/>
-    </row>
-    <row r="3" s="16" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="s">
+      <c r="AF2" s="12"/>
+    </row>
+    <row r="3" s="17" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>177198</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>198639</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>216945</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>228199</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>249640</v>
       </c>
-      <c r="G3" s="16" t="n">
+      <c r="G3" s="17" t="n">
         <v>274173</v>
       </c>
-      <c r="H3" s="16" t="n">
+      <c r="H3" s="17" t="n">
         <v>303776</v>
       </c>
-      <c r="I3" s="16" t="n">
+      <c r="I3" s="17" t="n">
         <v>333439</v>
       </c>
-      <c r="R3" s="16" t="n">
+      <c r="R3" s="17" t="n">
         <v>504874</v>
       </c>
-      <c r="S3" s="16" t="n">
+      <c r="S3" s="17" t="n">
         <v>749011</v>
       </c>
-      <c r="T3" s="16" t="n">
+      <c r="T3" s="17" t="n">
         <v>1055788</v>
       </c>
-      <c r="U3" s="16" t="n">
+      <c r="U3" s="17" t="n">
         <f aca="false">+T3*1.4</f>
         <v>1478103.2</v>
       </c>
-      <c r="V3" s="16" t="n">
+      <c r="V3" s="17" t="n">
         <f aca="false">+U3*1.4</f>
         <v>2069344.48</v>
       </c>
-      <c r="W3" s="16" t="n">
+      <c r="W3" s="17" t="n">
         <f aca="false">+V3*1.35</f>
         <v>2793615.048</v>
       </c>
-      <c r="X3" s="16" t="n">
-        <f aca="false">+W3*1.35</f>
-        <v>3771380.3148</v>
-      </c>
-      <c r="Y3" s="16" t="n">
-        <f aca="false">+X3*1.2</f>
-        <v>4525656.37776</v>
-      </c>
-      <c r="Z3" s="16" t="n">
+      <c r="X3" s="17" t="n">
+        <f aca="false">+W3*1.3</f>
+        <v>3631699.5624</v>
+      </c>
+      <c r="Y3" s="17" t="n">
+        <f aca="false">+X3*1.25</f>
+        <v>4539624.453</v>
+      </c>
+      <c r="Z3" s="17" t="n">
         <f aca="false">+Y3*1.2</f>
-        <v>5430787.653312</v>
-      </c>
-      <c r="AA3" s="16" t="n">
-        <f aca="false">+Z3*1.2</f>
-        <v>6516945.1839744</v>
-      </c>
-      <c r="AB3" s="16" t="n">
-        <f aca="false">+AA3*1.19</f>
-        <v>7755164.76892954</v>
-      </c>
-      <c r="AC3" s="16" t="n">
-        <f aca="false">+AB3*1.18</f>
-        <v>9151094.42733685</v>
-      </c>
-      <c r="AD3" s="16" t="n">
+        <v>5447549.3436</v>
+      </c>
+      <c r="AA3" s="17" t="n">
+        <f aca="false">+Z3*1.19</f>
+        <v>6482583.718884</v>
+      </c>
+      <c r="AB3" s="17" t="n">
+        <f aca="false">+AA3*1.18</f>
+        <v>7649448.78828312</v>
+      </c>
+      <c r="AC3" s="17" t="n">
+        <f aca="false">+AB3*1.17</f>
+        <v>8949855.08229125</v>
+      </c>
+      <c r="AD3" s="17" t="n">
         <f aca="false">+AC3*1.17</f>
-        <v>10706780.4799841</v>
-      </c>
-      <c r="AE3" s="16" t="n">
-        <f aca="false">+AD3*1.16</f>
-        <v>12419865.3567816</v>
-      </c>
-      <c r="AF3" s="17"/>
+        <v>10471330.4462808</v>
+      </c>
+      <c r="AE3" s="17" t="n">
+        <f aca="false">+AD3*1.17</f>
+        <v>12251456.6221485</v>
+      </c>
+      <c r="AF3" s="16"/>
     </row>
     <row r="4" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="19"/>
@@ -1593,11 +1581,11 @@
       </c>
       <c r="X4" s="18" t="n">
         <f aca="false">+X3/W3-1</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="Y4" s="18" t="n">
         <f aca="false">+Y3/X3-1</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" s="18" t="n">
         <f aca="false">+Z3/Y3-1</f>
@@ -1605,15 +1593,15 @@
       </c>
       <c r="AA4" s="18" t="n">
         <f aca="false">+AA3/Z3-1</f>
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="AB4" s="18" t="n">
         <f aca="false">+AB3/AA3-1</f>
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="AC4" s="18" t="n">
         <f aca="false">+AC3/AB3-1</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AD4" s="18" t="n">
         <f aca="false">+AD3/AC3-1</f>
@@ -1621,9 +1609,9 @@
       </c>
       <c r="AE4" s="18" t="n">
         <f aca="false">+AE3/AD3-1</f>
-        <v>0.16</v>
-      </c>
-      <c r="AF4" s="0"/>
+        <v>0.17</v>
+      </c>
+      <c r="AF4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -1676,35 +1664,35 @@
       </c>
       <c r="X5" s="3" t="n">
         <f aca="false">+X3-X7</f>
-        <v>584563.948794</v>
+        <v>562913.432172</v>
       </c>
       <c r="Y5" s="3" t="n">
         <f aca="false">+Y3-Y7</f>
-        <v>678848.456664</v>
+        <v>680943.66795</v>
       </c>
       <c r="Z5" s="3" t="n">
         <f aca="false">+Z3-Z7</f>
-        <v>787464.209730241</v>
+        <v>789894.654822</v>
       </c>
       <c r="AA5" s="3" t="n">
         <f aca="false">+AA3-AA7</f>
-        <v>912372.325756416</v>
+        <v>907561.72064376</v>
       </c>
       <c r="AB5" s="3" t="n">
         <f aca="false">+AB3-AB7</f>
-        <v>1046947.24380549</v>
+        <v>1032675.58641822</v>
       </c>
       <c r="AC5" s="3" t="n">
         <f aca="false">+AC3-AC7</f>
-        <v>1189642.27555379</v>
+        <v>1163481.16069786</v>
       </c>
       <c r="AD5" s="3" t="n">
         <f aca="false">+AD3-AD7</f>
-        <v>1338347.55999802</v>
+        <v>1308916.3057851</v>
       </c>
       <c r="AE5" s="3" t="n">
         <f aca="false">+AE3-AE7</f>
-        <v>1490383.84281379</v>
+        <v>1470174.79465782</v>
       </c>
     </row>
     <row r="6" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1749,11 +1737,11 @@
       </c>
       <c r="X6" s="18" t="n">
         <f aca="false">+X5/W5-1</f>
-        <v>0.3078125</v>
+        <v>0.259375</v>
       </c>
       <c r="Y6" s="18" t="n">
         <f aca="false">+Y5/X5-1</f>
-        <v>0.161290322580645</v>
+        <v>0.209677419354839</v>
       </c>
       <c r="Z6" s="18" t="n">
         <f aca="false">+Z5/Y5-1</f>
@@ -1761,15 +1749,15 @@
       </c>
       <c r="AA6" s="18" t="n">
         <f aca="false">+AA5/Z5-1</f>
-        <v>0.158620689655171</v>
+        <v>0.148965517241378</v>
       </c>
       <c r="AB6" s="18" t="n">
         <f aca="false">+AB5/AA5-1</f>
-        <v>0.147500000000001</v>
+        <v>0.137857142857143</v>
       </c>
       <c r="AC6" s="18" t="n">
         <f aca="false">+AC5/AB5-1</f>
-        <v>0.136296296296296</v>
+        <v>0.126666666666667</v>
       </c>
       <c r="AD6" s="18" t="n">
         <f aca="false">+AD5/AC5-1</f>
@@ -1777,9 +1765,9 @@
       </c>
       <c r="AE6" s="18" t="n">
         <f aca="false">+AE5/AD5-1</f>
-        <v>0.113599999999999</v>
-      </c>
-      <c r="AF6" s="0"/>
+        <v>0.1232</v>
+      </c>
+      <c r="AF6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -1855,35 +1843,35 @@
       </c>
       <c r="X7" s="3" t="n">
         <f aca="false">+X3*0.845</f>
-        <v>3186816.366006</v>
+        <v>3068786.130228</v>
       </c>
       <c r="Y7" s="3" t="n">
         <f aca="false">+Y3*0.85</f>
-        <v>3846807.921096</v>
+        <v>3858680.78505</v>
       </c>
       <c r="Z7" s="3" t="n">
         <f aca="false">+Z3*0.855</f>
-        <v>4643323.44358176</v>
+        <v>4657654.688778</v>
       </c>
       <c r="AA7" s="3" t="n">
         <f aca="false">+AA3*0.86</f>
-        <v>5604572.85821798</v>
+        <v>5575021.99824024</v>
       </c>
       <c r="AB7" s="3" t="n">
         <f aca="false">+AB3*0.865</f>
-        <v>6708217.52512405</v>
+        <v>6616773.2018649</v>
       </c>
       <c r="AC7" s="3" t="n">
         <f aca="false">+AC3*0.87</f>
-        <v>7961452.15178306</v>
+        <v>7786373.92159339</v>
       </c>
       <c r="AD7" s="3" t="n">
         <f aca="false">+AD3*0.875</f>
-        <v>9368432.9199861</v>
+        <v>9162414.14049566</v>
       </c>
       <c r="AE7" s="3" t="n">
         <f aca="false">+AE3*0.88</f>
-        <v>10929481.5139678</v>
+        <v>10781281.8274907</v>
       </c>
     </row>
     <row r="8" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1928,11 +1916,11 @@
       </c>
       <c r="X8" s="18" t="n">
         <f aca="false">+X7/W7-1</f>
-        <v>0.358035714285714</v>
+        <v>0.307738095238096</v>
       </c>
       <c r="Y8" s="18" t="n">
         <f aca="false">+Y7/X7-1</f>
-        <v>0.207100591715977</v>
+        <v>0.257396449704142</v>
       </c>
       <c r="Z8" s="18" t="n">
         <f aca="false">+Z7/Y7-1</f>
@@ -1940,15 +1928,15 @@
       </c>
       <c r="AA8" s="18" t="n">
         <f aca="false">+AA7/Z7-1</f>
-        <v>0.207017543859649</v>
+        <v>0.196959064327485</v>
       </c>
       <c r="AB8" s="18" t="n">
         <f aca="false">+AB7/AA7-1</f>
-        <v>0.196918604651163</v>
+        <v>0.186860465116279</v>
       </c>
       <c r="AC8" s="18" t="n">
         <f aca="false">+AC7/AB7-1</f>
-        <v>0.186820809248555</v>
+        <v>0.176763005780347</v>
       </c>
       <c r="AD8" s="18" t="n">
         <f aca="false">+AD7/AC7-1</f>
@@ -1956,9 +1944,9 @@
       </c>
       <c r="AE8" s="18" t="n">
         <f aca="false">+AE7/AD7-1</f>
-        <v>0.166628571428572</v>
-      </c>
-      <c r="AF8" s="0"/>
+        <v>0.176685714285714</v>
+      </c>
+      <c r="AF8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -2114,7 +2102,7 @@
         <f aca="false">+AE9/AD9-1</f>
         <v>0.05</v>
       </c>
-      <c r="AF10" s="0"/>
+      <c r="AF10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
@@ -2270,7 +2258,7 @@
         <f aca="false">+AE11/AD11-1</f>
         <v>0.05</v>
       </c>
-      <c r="AF12" s="0"/>
+      <c r="AF12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -2426,7 +2414,7 @@
         <f aca="false">+AE13/AD13-1</f>
         <v>0.05</v>
       </c>
-      <c r="AF14" s="0"/>
+      <c r="AF14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
@@ -2605,7 +2593,7 @@
         <f aca="false">+AE15/AD15-1</f>
         <v>0.05</v>
       </c>
-      <c r="AF16" s="0"/>
+      <c r="AF16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -2681,35 +2669,35 @@
       </c>
       <c r="X17" s="3" t="n">
         <f aca="false">+X7-X15</f>
-        <v>-1377567.603594</v>
+        <v>-1495597.839372</v>
       </c>
       <c r="Y17" s="3" t="n">
         <f aca="false">+Y7-Y15</f>
-        <v>-1286392.393944</v>
+        <v>-1274519.52999</v>
       </c>
       <c r="Z17" s="3" t="n">
         <f aca="false">+Z7-Z15</f>
-        <v>-1132431.54371424</v>
+        <v>-1118100.298518</v>
       </c>
       <c r="AA17" s="3" t="n">
         <f aca="false">+AA7-AA15</f>
-        <v>-748757.627807615</v>
+        <v>-778308.487785361</v>
       </c>
       <c r="AB17" s="3" t="n">
         <f aca="false">+AB7-AB15</f>
-        <v>37220.5147971679</v>
+        <v>-54223.8084619828</v>
       </c>
       <c r="AC17" s="3" t="n">
         <f aca="false">+AC7-AC15</f>
-        <v>956905.290939836</v>
+        <v>781827.060750165</v>
       </c>
       <c r="AD17" s="3" t="n">
         <f aca="false">+AD7-AD15</f>
-        <v>2013658.71610072</v>
+        <v>1807639.93661027</v>
       </c>
       <c r="AE17" s="3" t="n">
         <f aca="false">+AE7-AE15</f>
-        <v>3206968.59988813</v>
+        <v>3058768.91341101</v>
       </c>
     </row>
     <row r="18" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2754,37 +2742,37 @@
       </c>
       <c r="X18" s="18" t="n">
         <f aca="false">+X17/W17-1</f>
-        <v>-0.104574320832097</v>
+        <v>-0.027854090363457</v>
       </c>
       <c r="Y18" s="18" t="n">
         <f aca="false">+Y17/X17-1</f>
-        <v>-0.0661856517329015</v>
+        <v>-0.147819355953891</v>
       </c>
       <c r="Z18" s="18" t="n">
         <f aca="false">+Z17/Y17-1</f>
-        <v>-0.119684204411164</v>
+        <v>-0.122727998897927</v>
       </c>
       <c r="AA18" s="18" t="n">
         <f aca="false">+AA17/Z17-1</f>
-        <v>-0.338805394494946</v>
+        <v>-0.30390101065443</v>
       </c>
       <c r="AB18" s="18" t="n">
         <f aca="false">+AB17/AA17-1</f>
-        <v>-1.04970969698987</v>
+        <v>-0.930331212735102</v>
       </c>
       <c r="AC18" s="18" t="n">
         <f aca="false">+AC17/AB17-1</f>
-        <v>24.7090826431194</v>
+        <v>-15.4185198887001</v>
       </c>
       <c r="AD18" s="18" t="n">
         <f aca="false">+AD17/AC17-1</f>
-        <v>1.10434484495637</v>
+        <v>1.31207133566832</v>
       </c>
       <c r="AE18" s="18" t="n">
         <f aca="false">+AE17/AD17-1</f>
-        <v>0.592607810969161</v>
-      </c>
-      <c r="AF18" s="0"/>
+        <v>0.69213395403671</v>
+      </c>
+      <c r="AF18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -2929,7 +2917,7 @@
         <f aca="false">+AE19/AD19-1</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="0"/>
+      <c r="AF20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -3005,35 +2993,35 @@
       </c>
       <c r="X21" s="3" t="n">
         <f aca="false">+X17+X19</f>
-        <v>-1307567.603594</v>
+        <v>-1425597.839372</v>
       </c>
       <c r="Y21" s="3" t="n">
         <f aca="false">+Y17+Y19</f>
-        <v>-1216392.393944</v>
+        <v>-1204519.52999</v>
       </c>
       <c r="Z21" s="3" t="n">
         <f aca="false">+Z17+Z19</f>
-        <v>-1062431.54371424</v>
+        <v>-1048100.298518</v>
       </c>
       <c r="AA21" s="3" t="n">
         <f aca="false">+AA17+AA19</f>
-        <v>-678757.627807615</v>
+        <v>-708308.487785361</v>
       </c>
       <c r="AB21" s="3" t="n">
         <f aca="false">+AB17+AB19</f>
-        <v>107220.514797168</v>
+        <v>15776.1915380172</v>
       </c>
       <c r="AC21" s="3" t="n">
         <f aca="false">+AC17+AC19</f>
-        <v>1026905.29093984</v>
+        <v>851827.060750165</v>
       </c>
       <c r="AD21" s="3" t="n">
         <f aca="false">+AD17+AD19</f>
-        <v>2083658.71610072</v>
+        <v>1877639.93661027</v>
       </c>
       <c r="AE21" s="3" t="n">
         <f aca="false">+AE17+AE19</f>
-        <v>3276968.59988813</v>
+        <v>3128768.91341101</v>
       </c>
     </row>
     <row r="22" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3078,37 +3066,37 @@
       </c>
       <c r="X22" s="18" t="n">
         <f aca="false">+X21/W21-1</f>
-        <v>-0.109559306796414</v>
+        <v>-0.0291818756974263</v>
       </c>
       <c r="Y22" s="18" t="n">
         <f aca="false">+Y21/X21-1</f>
-        <v>-0.0697288686255262</v>
+        <v>-0.15507761254702</v>
       </c>
       <c r="Z22" s="18" t="n">
         <f aca="false">+Z21/Y21-1</f>
-        <v>-0.126571697584002</v>
+        <v>-0.129860270072414</v>
       </c>
       <c r="AA22" s="18" t="n">
         <f aca="false">+AA21/Z21-1</f>
-        <v>-0.361128129314862</v>
+        <v>-0.324197799784144</v>
       </c>
       <c r="AB22" s="18" t="n">
         <f aca="false">+AB21/AA21-1</f>
-        <v>-1.15796583405403</v>
+        <v>-1.02227305165768</v>
       </c>
       <c r="AC22" s="18" t="n">
         <f aca="false">+AC21/AB21-1</f>
-        <v>8.57750755890757</v>
+        <v>52.9944674668436</v>
       </c>
       <c r="AD22" s="18" t="n">
         <f aca="false">+AD21/AC21-1</f>
-        <v>1.02906610228264</v>
+        <v>1.20425016194804</v>
       </c>
       <c r="AE22" s="18" t="n">
         <f aca="false">+AE21/AD21-1</f>
-        <v>0.572699297906393</v>
-      </c>
-      <c r="AF22" s="0"/>
+        <v>0.66633061664603</v>
+      </c>
+      <c r="AF22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
@@ -3161,15 +3149,15 @@
       </c>
       <c r="AC23" s="3" t="n">
         <f aca="false">+AC21*(0.22)</f>
-        <v>225919.164006764</v>
+        <v>187401.953365036</v>
       </c>
       <c r="AD23" s="3" t="n">
         <f aca="false">+AD21*(0.22)</f>
-        <v>458404.917542157</v>
+        <v>413080.78605426</v>
       </c>
       <c r="AE23" s="3" t="n">
         <f aca="false">+AE21*(0.22)</f>
-        <v>720933.091975389</v>
+        <v>688329.160950422</v>
       </c>
     </row>
     <row r="24" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3237,13 +3225,13 @@
       </c>
       <c r="AD24" s="18" t="n">
         <f aca="false">+AD23/AC23-1</f>
-        <v>1.02906610228264</v>
+        <v>1.20425016194804</v>
       </c>
       <c r="AE24" s="18" t="n">
         <f aca="false">+AE23/AD23-1</f>
-        <v>0.572699297906393</v>
-      </c>
-      <c r="AF24" s="0"/>
+        <v>0.66633061664603</v>
+      </c>
+      <c r="AF24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
@@ -3319,35 +3307,35 @@
       </c>
       <c r="X25" s="3" t="n">
         <f aca="false">+X21-X23</f>
-        <v>-1307567.603594</v>
+        <v>-1425597.839372</v>
       </c>
       <c r="Y25" s="3" t="n">
         <f aca="false">+Y21-Y23</f>
-        <v>-1216392.393944</v>
+        <v>-1204519.52999</v>
       </c>
       <c r="Z25" s="3" t="n">
         <f aca="false">+Z21-Z23</f>
-        <v>-1062431.54371424</v>
+        <v>-1048100.298518</v>
       </c>
       <c r="AA25" s="3" t="n">
         <f aca="false">+AA21-AA23</f>
-        <v>-678757.627807615</v>
+        <v>-708308.487785361</v>
       </c>
       <c r="AB25" s="3" t="n">
         <f aca="false">+AB21-AB23</f>
-        <v>107220.514797168</v>
+        <v>15776.1915380172</v>
       </c>
       <c r="AC25" s="3" t="n">
         <f aca="false">+AC21-AC23</f>
-        <v>800986.126933072</v>
+        <v>664425.107385129</v>
       </c>
       <c r="AD25" s="3" t="n">
         <f aca="false">+AD21-AD23</f>
-        <v>1625253.79855856</v>
+        <v>1464559.15055601</v>
       </c>
       <c r="AE25" s="3" t="n">
         <f aca="false">+AE21-AE23</f>
-        <v>2556035.50791274</v>
+        <v>2440439.75246059</v>
       </c>
     </row>
     <row r="26" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3392,37 +3380,37 @@
       </c>
       <c r="X26" s="18" t="n">
         <f aca="false">+X25/W25-1</f>
-        <v>-0.190508460724013</v>
+        <v>-0.117438068815842</v>
       </c>
       <c r="Y26" s="18" t="n">
         <f aca="false">+Y25/X25-1</f>
-        <v>-0.0697288686255262</v>
+        <v>-0.15507761254702</v>
       </c>
       <c r="Z26" s="18" t="n">
         <f aca="false">+Z25/Y25-1</f>
-        <v>-0.126571697584002</v>
+        <v>-0.129860270072414</v>
       </c>
       <c r="AA26" s="18" t="n">
         <f aca="false">+AA25/Z25-1</f>
-        <v>-0.361128129314862</v>
+        <v>-0.324197799784144</v>
       </c>
       <c r="AB26" s="18" t="n">
         <f aca="false">+AB25/AA25-1</f>
-        <v>-1.15796583405403</v>
+        <v>-1.02227305165768</v>
       </c>
       <c r="AC26" s="18" t="n">
         <f aca="false">+AC25/AB25-1</f>
-        <v>6.4704558959479</v>
+        <v>41.115684624138</v>
       </c>
       <c r="AD26" s="18" t="n">
         <f aca="false">+AD25/AC25-1</f>
-        <v>1.02906610228264</v>
+        <v>1.20425016194804</v>
       </c>
       <c r="AE26" s="18" t="n">
         <f aca="false">+AE25/AD25-1</f>
-        <v>0.572699297906393</v>
-      </c>
-      <c r="AF26" s="0"/>
+        <v>0.66633061664603</v>
+      </c>
+      <c r="AF26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
@@ -3521,391 +3509,391 @@
       <c r="T28" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="AF28" s="0"/>
-    </row>
-    <row r="29" s="16" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="s">
+      <c r="AF28" s="12"/>
+    </row>
+    <row r="29" s="17" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <f aca="false">+B25+B27</f>
         <v>-827854</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <f aca="false">+C25+C27</f>
         <v>-15598</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <f aca="false">+D25+D27</f>
         <v>33070</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <f aca="false">+E25+E27</f>
         <v>8611</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <f aca="false">+F25+F27</f>
         <v>846</v>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="G29" s="17" t="n">
         <f aca="false">+G25+G27</f>
         <v>-1097015</v>
       </c>
-      <c r="H29" s="16" t="n">
+      <c r="H29" s="17" t="n">
         <f aca="false">+H25+H27</f>
         <v>-226557</v>
       </c>
-      <c r="I29" s="16" t="n">
+      <c r="I29" s="17" t="n">
         <f aca="false">+I25+I27</f>
         <v>-142401</v>
       </c>
-      <c r="J29" s="16" t="n">
+      <c r="J29" s="17" t="n">
         <f aca="false">+J25+J27</f>
         <v>0</v>
       </c>
-      <c r="K29" s="16" t="n">
+      <c r="K29" s="17" t="n">
         <f aca="false">+K25+K27</f>
         <v>0</v>
       </c>
-      <c r="L29" s="16" t="n">
+      <c r="L29" s="17" t="n">
         <f aca="false">+L25+L27</f>
         <v>0</v>
       </c>
-      <c r="R29" s="16" t="n">
+      <c r="R29" s="17" t="n">
         <f aca="false">+R25+R27</f>
         <v>285859</v>
       </c>
-      <c r="S29" s="16" t="n">
+      <c r="S29" s="17" t="n">
         <f aca="false">+S25+S27</f>
         <v>-732120</v>
       </c>
-      <c r="T29" s="16" t="n">
+      <c r="T29" s="17" t="n">
         <f aca="false">+T25+T27</f>
         <v>-1250463</v>
       </c>
-      <c r="U29" s="16" t="n">
+      <c r="U29" s="17" t="n">
         <f aca="false">+U25+U27</f>
         <v>-1482273.0384</v>
       </c>
-      <c r="V29" s="16" t="n">
+      <c r="V29" s="17" t="n">
         <f aca="false">+V25+V27</f>
         <v>-1583636.48212</v>
       </c>
-      <c r="W29" s="16" t="n">
+      <c r="W29" s="17" t="n">
         <f aca="false">+W25+W27</f>
         <v>-1615294.960048</v>
       </c>
-      <c r="X29" s="16" t="n">
+      <c r="X29" s="17" t="n">
         <f aca="false">+X25+X27</f>
-        <v>-1307567.603594</v>
-      </c>
-      <c r="Y29" s="16" t="n">
+        <v>-1425597.839372</v>
+      </c>
+      <c r="Y29" s="17" t="n">
         <f aca="false">+Y25+Y27</f>
-        <v>-1216392.393944</v>
-      </c>
-      <c r="Z29" s="16" t="n">
+        <v>-1204519.52999</v>
+      </c>
+      <c r="Z29" s="17" t="n">
         <f aca="false">+Z25+Z27</f>
-        <v>-1062431.54371424</v>
-      </c>
-      <c r="AA29" s="16" t="n">
+        <v>-1048100.298518</v>
+      </c>
+      <c r="AA29" s="17" t="n">
         <f aca="false">+AA25+AA27</f>
-        <v>-678757.627807615</v>
-      </c>
-      <c r="AB29" s="16" t="n">
+        <v>-708308.487785361</v>
+      </c>
+      <c r="AB29" s="17" t="n">
         <f aca="false">+AB25+AB27</f>
-        <v>107220.514797168</v>
-      </c>
-      <c r="AC29" s="16" t="n">
+        <v>15776.1915380172</v>
+      </c>
+      <c r="AC29" s="17" t="n">
         <f aca="false">+AC25+AC27</f>
-        <v>800986.126933072</v>
-      </c>
-      <c r="AD29" s="16" t="n">
+        <v>664425.107385129</v>
+      </c>
+      <c r="AD29" s="17" t="n">
         <f aca="false">+AD25+AD27</f>
-        <v>1625253.79855856</v>
-      </c>
-      <c r="AE29" s="16" t="n">
+        <v>1464559.15055601</v>
+      </c>
+      <c r="AE29" s="17" t="n">
         <f aca="false">+AE25+AE27</f>
-        <v>2556035.50791274</v>
-      </c>
-      <c r="AF29" s="21" t="n">
+        <v>2440439.75246059</v>
+      </c>
+      <c r="AF29" s="17" t="n">
         <f aca="false">+AE29*(1+$AJ$36)</f>
-        <v>2581595.86299187</v>
-      </c>
-      <c r="AG29" s="21" t="n">
+        <v>2464844.14998519</v>
+      </c>
+      <c r="AG29" s="17" t="n">
         <f aca="false">+AF29*(1+$AJ$36)</f>
-        <v>2607411.82162179</v>
-      </c>
-      <c r="AH29" s="21" t="n">
+        <v>2489492.59148505</v>
+      </c>
+      <c r="AH29" s="17" t="n">
         <f aca="false">+AG29*(1+$AJ$36)</f>
-        <v>2633485.93983801</v>
-      </c>
-      <c r="AI29" s="21" t="n">
+        <v>2514387.5173999</v>
+      </c>
+      <c r="AI29" s="17" t="n">
         <f aca="false">+AH29*(1+$AJ$36)</f>
-        <v>2659820.79923639</v>
-      </c>
-      <c r="AJ29" s="21" t="n">
+        <v>2539531.39257389</v>
+      </c>
+      <c r="AJ29" s="17" t="n">
         <f aca="false">+AI29*(1+$AJ$36)</f>
-        <v>2686419.00722875</v>
-      </c>
-      <c r="AK29" s="21" t="n">
+        <v>2564926.70649963</v>
+      </c>
+      <c r="AK29" s="17" t="n">
         <f aca="false">+AJ29*(1+$AJ$36)</f>
-        <v>2713283.19730104</v>
-      </c>
-      <c r="AL29" s="21" t="n">
+        <v>2590575.97356463</v>
+      </c>
+      <c r="AL29" s="17" t="n">
         <f aca="false">+AK29*(1+$AJ$36)</f>
-        <v>2740416.02927405</v>
-      </c>
-      <c r="AM29" s="21" t="n">
+        <v>2616481.73330028</v>
+      </c>
+      <c r="AM29" s="17" t="n">
         <f aca="false">+AL29*(1+$AJ$36)</f>
-        <v>2767820.18956679</v>
-      </c>
-      <c r="AN29" s="21" t="n">
+        <v>2642646.55063328</v>
+      </c>
+      <c r="AN29" s="17" t="n">
         <f aca="false">+AM29*(1+$AJ$36)</f>
-        <v>2795498.39146246</v>
-      </c>
-      <c r="AO29" s="21" t="n">
+        <v>2669073.01613961</v>
+      </c>
+      <c r="AO29" s="17" t="n">
         <f aca="false">+AN29*(1+$AJ$36)</f>
-        <v>2823453.37537708</v>
-      </c>
-      <c r="AP29" s="21" t="n">
+        <v>2695763.74630101</v>
+      </c>
+      <c r="AP29" s="17" t="n">
         <f aca="false">+AO29*(1+$AJ$36)</f>
-        <v>2851687.90913085</v>
-      </c>
-      <c r="AQ29" s="21" t="n">
+        <v>2722721.38376402</v>
+      </c>
+      <c r="AQ29" s="17" t="n">
         <f aca="false">+AP29*(1+$AJ$36)</f>
-        <v>2880204.78822216</v>
-      </c>
-      <c r="AR29" s="21" t="n">
+        <v>2749948.59760166</v>
+      </c>
+      <c r="AR29" s="17" t="n">
         <f aca="false">+AQ29*(1+$AJ$36)</f>
-        <v>2909006.83610438</v>
-      </c>
-      <c r="AS29" s="21" t="n">
+        <v>2777448.08357768</v>
+      </c>
+      <c r="AS29" s="17" t="n">
         <f aca="false">+AR29*(1+$AJ$36)</f>
-        <v>2938096.90446543</v>
-      </c>
-      <c r="AT29" s="21" t="n">
+        <v>2805222.56441345</v>
+      </c>
+      <c r="AT29" s="17" t="n">
         <f aca="false">+AS29*(1+$AJ$36)</f>
-        <v>2967477.87351008</v>
-      </c>
-      <c r="AU29" s="21" t="n">
+        <v>2833274.79005759</v>
+      </c>
+      <c r="AU29" s="17" t="n">
         <f aca="false">+AT29*(1+$AJ$36)</f>
-        <v>2997152.65224518</v>
-      </c>
-      <c r="AV29" s="21" t="n">
+        <v>2861607.53795816</v>
+      </c>
+      <c r="AV29" s="17" t="n">
         <f aca="false">+AU29*(1+$AJ$36)</f>
-        <v>3027124.17876763</v>
-      </c>
-      <c r="AW29" s="21" t="n">
+        <v>2890223.61333774</v>
+      </c>
+      <c r="AW29" s="17" t="n">
         <f aca="false">+AV29*(1+$AJ$36)</f>
-        <v>3057395.42055531</v>
-      </c>
-      <c r="AX29" s="21" t="n">
+        <v>2919125.84947112</v>
+      </c>
+      <c r="AX29" s="17" t="n">
         <f aca="false">+AW29*(1+$AJ$36)</f>
-        <v>3087969.37476086</v>
-      </c>
-      <c r="AY29" s="21" t="n">
+        <v>2948317.10796583</v>
+      </c>
+      <c r="AY29" s="17" t="n">
         <f aca="false">+AX29*(1+$AJ$36)</f>
-        <v>3118849.06850847</v>
-      </c>
-      <c r="AZ29" s="21" t="n">
+        <v>2977800.27904549</v>
+      </c>
+      <c r="AZ29" s="17" t="n">
         <f aca="false">+AY29*(1+$AJ$36)</f>
-        <v>3150037.55919355</v>
-      </c>
-      <c r="BA29" s="21" t="n">
+        <v>3007578.28183595</v>
+      </c>
+      <c r="BA29" s="17" t="n">
         <f aca="false">+AZ29*(1+$AJ$36)</f>
-        <v>3181537.93478549</v>
-      </c>
-      <c r="BB29" s="21" t="n">
+        <v>3037654.0646543</v>
+      </c>
+      <c r="BB29" s="17" t="n">
         <f aca="false">+BA29*(1+$AJ$36)</f>
-        <v>3213353.31413334</v>
-      </c>
-      <c r="BC29" s="21" t="n">
+        <v>3068030.60530085</v>
+      </c>
+      <c r="BC29" s="17" t="n">
         <f aca="false">+BB29*(1+$AJ$36)</f>
-        <v>3245486.84727468</v>
-      </c>
-      <c r="BD29" s="21" t="n">
+        <v>3098710.91135386</v>
+      </c>
+      <c r="BD29" s="17" t="n">
         <f aca="false">+BC29*(1+$AJ$36)</f>
-        <v>3277941.71574743</v>
-      </c>
-      <c r="BE29" s="21" t="n">
+        <v>3129698.0204674</v>
+      </c>
+      <c r="BE29" s="17" t="n">
         <f aca="false">+BD29*(1+$AJ$36)</f>
-        <v>3310721.1329049</v>
-      </c>
-      <c r="BF29" s="21" t="n">
+        <v>3160995.00067207</v>
+      </c>
+      <c r="BF29" s="17" t="n">
         <f aca="false">+BE29*(1+$AJ$36)</f>
-        <v>3343828.34423395</v>
-      </c>
-      <c r="BG29" s="21" t="n">
+        <v>3192604.95067879</v>
+      </c>
+      <c r="BG29" s="17" t="n">
         <f aca="false">+BF29*(1+$AJ$36)</f>
-        <v>3377266.62767629</v>
-      </c>
-      <c r="BH29" s="21" t="n">
+        <v>3224531.00018558</v>
+      </c>
+      <c r="BH29" s="17" t="n">
         <f aca="false">+BG29*(1+$AJ$36)</f>
-        <v>3411039.29395305</v>
-      </c>
-      <c r="BI29" s="21" t="n">
+        <v>3256776.31018743</v>
+      </c>
+      <c r="BI29" s="17" t="n">
         <f aca="false">+BH29*(1+$AJ$36)</f>
-        <v>3445149.68689258</v>
-      </c>
-      <c r="BJ29" s="21" t="n">
+        <v>3289344.07328931</v>
+      </c>
+      <c r="BJ29" s="17" t="n">
         <f aca="false">+BI29*(1+$AJ$36)</f>
-        <v>3479601.18376151</v>
-      </c>
-      <c r="BK29" s="21" t="n">
+        <v>3322237.5140222</v>
+      </c>
+      <c r="BK29" s="17" t="n">
         <f aca="false">+BJ29*(1+$AJ$36)</f>
-        <v>3514397.19559912</v>
-      </c>
-      <c r="BL29" s="21" t="n">
+        <v>3355459.88916242</v>
+      </c>
+      <c r="BL29" s="17" t="n">
         <f aca="false">+BK29*(1+$AJ$36)</f>
-        <v>3549541.16755511</v>
-      </c>
-      <c r="BM29" s="21" t="n">
+        <v>3389014.48805405</v>
+      </c>
+      <c r="BM29" s="17" t="n">
         <f aca="false">+BL29*(1+$AJ$36)</f>
-        <v>3585036.57923066</v>
-      </c>
-      <c r="BN29" s="21" t="n">
+        <v>3422904.63293459</v>
+      </c>
+      <c r="BN29" s="17" t="n">
         <f aca="false">+BM29*(1+$AJ$36)</f>
-        <v>3620886.94502297</v>
-      </c>
-      <c r="BO29" s="21" t="n">
+        <v>3457133.67926393</v>
+      </c>
+      <c r="BO29" s="17" t="n">
         <f aca="false">+BN29*(1+$AJ$36)</f>
-        <v>3657095.8144732</v>
-      </c>
-      <c r="BP29" s="21" t="n">
+        <v>3491705.01605657</v>
+      </c>
+      <c r="BP29" s="17" t="n">
         <f aca="false">+BO29*(1+$AJ$36)</f>
-        <v>3693666.77261793</v>
-      </c>
-      <c r="BQ29" s="21" t="n">
+        <v>3526622.06621714</v>
+      </c>
+      <c r="BQ29" s="17" t="n">
         <f aca="false">+BP29*(1+$AJ$36)</f>
-        <v>3730603.44034411</v>
-      </c>
-      <c r="BR29" s="21" t="n">
+        <v>3561888.28687931</v>
+      </c>
+      <c r="BR29" s="17" t="n">
         <f aca="false">+BQ29*(1+$AJ$36)</f>
-        <v>3767909.47474755</v>
-      </c>
-      <c r="BS29" s="21" t="n">
+        <v>3597507.1697481</v>
+      </c>
+      <c r="BS29" s="17" t="n">
         <f aca="false">+BR29*(1+$AJ$36)</f>
-        <v>3805588.56949503</v>
-      </c>
-      <c r="BT29" s="21" t="n">
+        <v>3633482.24144559</v>
+      </c>
+      <c r="BT29" s="17" t="n">
         <f aca="false">+BS29*(1+$AJ$36)</f>
-        <v>3843644.45518998</v>
-      </c>
-      <c r="BU29" s="21" t="n">
+        <v>3669817.06386004</v>
+      </c>
+      <c r="BU29" s="17" t="n">
         <f aca="false">+BT29*(1+$AJ$36)</f>
-        <v>3882080.89974188</v>
-      </c>
-      <c r="BV29" s="21" t="n">
+        <v>3706515.23449864</v>
+      </c>
+      <c r="BV29" s="17" t="n">
         <f aca="false">+BU29*(1+$AJ$36)</f>
-        <v>3920901.7087393</v>
-      </c>
-      <c r="BW29" s="21" t="n">
+        <v>3743580.38684363</v>
+      </c>
+      <c r="BW29" s="17" t="n">
         <f aca="false">+BV29*(1+$AJ$36)</f>
-        <v>3960110.72582669</v>
-      </c>
-      <c r="BX29" s="21" t="n">
+        <v>3781016.19071206</v>
+      </c>
+      <c r="BX29" s="17" t="n">
         <f aca="false">+BW29*(1+$AJ$36)</f>
-        <v>3999711.83308496</v>
-      </c>
-      <c r="BY29" s="21" t="n">
+        <v>3818826.35261918</v>
+      </c>
+      <c r="BY29" s="17" t="n">
         <f aca="false">+BX29*(1+$AJ$36)</f>
-        <v>4039708.95141581</v>
-      </c>
-      <c r="BZ29" s="21" t="n">
+        <v>3857014.61614538</v>
+      </c>
+      <c r="BZ29" s="17" t="n">
         <f aca="false">+BY29*(1+$AJ$36)</f>
-        <v>4080106.04092997</v>
-      </c>
-      <c r="CA29" s="21" t="n">
+        <v>3895584.76230683</v>
+      </c>
+      <c r="CA29" s="17" t="n">
         <f aca="false">+BZ29*(1+$AJ$36)</f>
-        <v>4120907.10133927</v>
-      </c>
-      <c r="CB29" s="21" t="n">
+        <v>3934540.6099299</v>
+      </c>
+      <c r="CB29" s="17" t="n">
         <f aca="false">+CA29*(1+$AJ$36)</f>
-        <v>4162116.17235266</v>
-      </c>
-      <c r="CC29" s="21" t="n">
+        <v>3973886.0160292</v>
+      </c>
+      <c r="CC29" s="17" t="n">
         <f aca="false">+CB29*(1+$AJ$36)</f>
-        <v>4203737.33407618</v>
-      </c>
-      <c r="CD29" s="21" t="n">
+        <v>4013624.87618949</v>
+      </c>
+      <c r="CD29" s="17" t="n">
         <f aca="false">+CC29*(1+$AJ$36)</f>
-        <v>4245774.70741695</v>
-      </c>
-      <c r="CE29" s="21" t="n">
+        <v>4053761.12495139</v>
+      </c>
+      <c r="CE29" s="17" t="n">
         <f aca="false">+CD29*(1+$AJ$36)</f>
-        <v>4288232.45449112</v>
-      </c>
-      <c r="CF29" s="21" t="n">
+        <v>4094298.7362009</v>
+      </c>
+      <c r="CF29" s="17" t="n">
         <f aca="false">+CE29*(1+$AJ$36)</f>
-        <v>4331114.77903603</v>
-      </c>
-      <c r="CG29" s="21" t="n">
+        <v>4135241.72356291</v>
+      </c>
+      <c r="CG29" s="17" t="n">
         <f aca="false">+CF29*(1+$AJ$36)</f>
-        <v>4374425.92682639</v>
-      </c>
-      <c r="CH29" s="21" t="n">
+        <v>4176594.14079854</v>
+      </c>
+      <c r="CH29" s="17" t="n">
         <f aca="false">+CG29*(1+$AJ$36)</f>
-        <v>4418170.18609465</v>
-      </c>
-      <c r="CI29" s="21" t="n">
+        <v>4218360.08220652</v>
+      </c>
+      <c r="CI29" s="17" t="n">
         <f aca="false">+CH29*(1+$AJ$36)</f>
-        <v>4462351.8879556</v>
-      </c>
-      <c r="CJ29" s="21" t="n">
+        <v>4260543.68302859</v>
+      </c>
+      <c r="CJ29" s="17" t="n">
         <f aca="false">+CI29*(1+$AJ$36)</f>
-        <v>4506975.40683515</v>
-      </c>
-      <c r="CK29" s="21" t="n">
+        <v>4303149.11985887</v>
+      </c>
+      <c r="CK29" s="17" t="n">
         <f aca="false">+CJ29*(1+$AJ$36)</f>
-        <v>4552045.16090351</v>
-      </c>
-      <c r="CL29" s="21" t="n">
+        <v>4346180.61105746</v>
+      </c>
+      <c r="CL29" s="17" t="n">
         <f aca="false">+CK29*(1+$AJ$36)</f>
-        <v>4597565.61251254</v>
-      </c>
-      <c r="CM29" s="21" t="n">
+        <v>4389642.41716804</v>
+      </c>
+      <c r="CM29" s="17" t="n">
         <f aca="false">+CL29*(1+$AJ$36)</f>
-        <v>4643541.26863767</v>
-      </c>
-      <c r="CN29" s="21" t="n">
+        <v>4433538.84133972</v>
+      </c>
+      <c r="CN29" s="17" t="n">
         <f aca="false">+CM29*(1+$AJ$36)</f>
-        <v>4689976.68132404</v>
-      </c>
-      <c r="CO29" s="21" t="n">
+        <v>4477874.22975312</v>
+      </c>
+      <c r="CO29" s="17" t="n">
         <f aca="false">+CN29*(1+$AJ$36)</f>
-        <v>4736876.44813728</v>
-      </c>
-      <c r="CP29" s="21" t="n">
+        <v>4522652.97205065</v>
+      </c>
+      <c r="CP29" s="17" t="n">
         <f aca="false">+CO29*(1+$AJ$36)</f>
-        <v>4784245.21261866</v>
-      </c>
-      <c r="CQ29" s="21" t="n">
+        <v>4567879.50177115</v>
+      </c>
+      <c r="CQ29" s="17" t="n">
         <f aca="false">+CP29*(1+$AJ$36)</f>
-        <v>4832087.66474484</v>
-      </c>
-      <c r="CR29" s="21" t="n">
+        <v>4613558.29678887</v>
+      </c>
+      <c r="CR29" s="17" t="n">
         <f aca="false">+CQ29*(1+$AJ$36)</f>
-        <v>4880408.54139229</v>
-      </c>
-      <c r="CS29" s="21" t="n">
+        <v>4659693.87975675</v>
+      </c>
+      <c r="CS29" s="17" t="n">
         <f aca="false">+CR29*(1+$AJ$36)</f>
-        <v>4929212.62680621</v>
-      </c>
-      <c r="CT29" s="21" t="n">
+        <v>4706290.81855432</v>
+      </c>
+      <c r="CT29" s="17" t="n">
         <f aca="false">+CS29*(1+$AJ$36)</f>
-        <v>4978504.75307427</v>
-      </c>
-      <c r="CU29" s="21" t="n">
+        <v>4753353.72673987</v>
+      </c>
+      <c r="CU29" s="17" t="n">
         <f aca="false">+CT29*(1+$AJ$36)</f>
-        <v>5028289.80060502</v>
-      </c>
-      <c r="CV29" s="21" t="n">
+        <v>4800887.26400726</v>
+      </c>
+      <c r="CV29" s="17" t="n">
         <f aca="false">+CU29*(1+$AJ$36)</f>
-        <v>5078572.69861107</v>
-      </c>
-      <c r="CW29" s="21" t="n">
+        <v>4848896.13664734</v>
+      </c>
+      <c r="CW29" s="17" t="n">
         <f aca="false">+CV29*(1+$AJ$36)</f>
-        <v>5129358.42559718</v>
+        <v>4897385.09801381</v>
       </c>
     </row>
     <row r="30" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3950,131 +3938,131 @@
       </c>
       <c r="X30" s="18" t="n">
         <f aca="false">+X29/W29-1</f>
-        <v>-0.190508460724013</v>
+        <v>-0.117438068815842</v>
       </c>
       <c r="Y30" s="18" t="n">
         <f aca="false">+Y29/X29-1</f>
-        <v>-0.0697288686255262</v>
+        <v>-0.15507761254702</v>
       </c>
       <c r="Z30" s="18" t="n">
         <f aca="false">+Z29/Y29-1</f>
-        <v>-0.126571697584002</v>
+        <v>-0.129860270072414</v>
       </c>
       <c r="AA30" s="18" t="n">
         <f aca="false">+AA29/Z29-1</f>
-        <v>-0.361128129314862</v>
+        <v>-0.324197799784144</v>
       </c>
       <c r="AB30" s="18" t="n">
         <f aca="false">+AB29/AA29-1</f>
-        <v>-1.15796583405403</v>
+        <v>-1.02227305165768</v>
       </c>
       <c r="AC30" s="18" t="n">
         <f aca="false">+AC29/AB29-1</f>
-        <v>6.4704558959479</v>
+        <v>41.115684624138</v>
       </c>
       <c r="AD30" s="18" t="n">
         <f aca="false">+AD29/AC29-1</f>
-        <v>1.02906610228264</v>
+        <v>1.20425016194804</v>
       </c>
       <c r="AE30" s="18" t="n">
         <f aca="false">+AE29/AD29-1</f>
-        <v>0.572699297906393</v>
-      </c>
-      <c r="AF30" s="0"/>
-    </row>
-    <row r="31" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
+        <v>0.66633061664603</v>
+      </c>
+      <c r="AF30" s="12"/>
+    </row>
+    <row r="31" s="21" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="21" t="n">
         <f aca="false">+B29/B33</f>
         <v>-4.38523799938553</v>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="21" t="n">
         <f aca="false">+C29/C33</f>
         <v>-0.0740055416381994</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="21" t="n">
         <f aca="false">+D29/D33</f>
         <v>0.145724546676361</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="21" t="n">
         <f aca="false">+E29/E33</f>
         <v>0.0372647959978535</v>
       </c>
-      <c r="F31" s="22" t="n">
+      <c r="F31" s="21" t="n">
         <f aca="false">+F29/F33</f>
         <v>0.00365124168112489</v>
       </c>
-      <c r="G31" s="22" t="n">
+      <c r="G31" s="21" t="n">
         <f aca="false">+G29/G33</f>
         <v>-2.7206903564378</v>
       </c>
-      <c r="H31" s="22" t="n">
+      <c r="H31" s="21" t="n">
         <f aca="false">+H29/H33</f>
         <v>-0.443328845717327</v>
       </c>
-      <c r="I31" s="22" t="n">
+      <c r="I31" s="21" t="n">
         <f aca="false">+I29/I33</f>
         <v>-0.272024986389295</v>
       </c>
-      <c r="R31" s="22" t="n">
+      <c r="R31" s="21" t="n">
         <f aca="false">+R29/R33</f>
         <v>1.52696747450683</v>
       </c>
-      <c r="S31" s="22" t="n">
+      <c r="S31" s="21" t="n">
         <f aca="false">+S29/S33</f>
         <v>-3.74271517084841</v>
       </c>
-      <c r="T31" s="22" t="n">
+      <c r="T31" s="21" t="n">
         <f aca="false">+T29/T33</f>
         <v>-3.71008829707694</v>
       </c>
-      <c r="U31" s="22" t="n">
+      <c r="U31" s="21" t="n">
         <f aca="false">+U29/U33</f>
         <v>-3.99805646740485</v>
       </c>
-      <c r="V31" s="22" t="n">
+      <c r="V31" s="21" t="n">
         <f aca="false">+V29/V33</f>
         <v>-3.88314428113513</v>
       </c>
-      <c r="W31" s="22" t="n">
+      <c r="W31" s="21" t="n">
         <f aca="false">+W29/W33</f>
         <v>-3.60070201904139</v>
       </c>
-      <c r="X31" s="22" t="n">
+      <c r="X31" s="21" t="n">
         <f aca="false">+X29/X33</f>
-        <v>-2.64976165442542</v>
-      </c>
-      <c r="Y31" s="22" t="n">
+        <v>-2.8889477523126</v>
+      </c>
+      <c r="Y31" s="21" t="n">
         <f aca="false">+Y29/Y33</f>
-        <v>-2.48989572942933</v>
-      </c>
-      <c r="Z31" s="22" t="n">
+        <v>-2.46559255768776</v>
+      </c>
+      <c r="Z31" s="21" t="n">
         <f aca="false">+Z29/Z33</f>
-        <v>-2.19671252540233</v>
-      </c>
-      <c r="AA31" s="22" t="n">
+        <v>-2.16708085076555</v>
+      </c>
+      <c r="AA31" s="21" t="n">
         <f aca="false">+AA29/AA33</f>
-        <v>-1.4175937782437</v>
-      </c>
-      <c r="AB31" s="22" t="n">
+        <v>-1.47931111817475</v>
+      </c>
+      <c r="AB31" s="21" t="n">
         <f aca="false">+AB29/AB33</f>
-        <v>0.226193316697046</v>
-      </c>
-      <c r="AC31" s="22" t="n">
+        <v>0.0332815888413011</v>
+      </c>
+      <c r="AC31" s="21" t="n">
         <f aca="false">+AC29/AC33</f>
-        <v>1.70683555186208</v>
-      </c>
-      <c r="AD31" s="22" t="n">
+        <v>1.41583525194997</v>
+      </c>
+      <c r="AD31" s="21" t="n">
         <f aca="false">+AD29/AD33</f>
-        <v>3.49826480853962</v>
-      </c>
-      <c r="AE31" s="22" t="n">
+        <v>3.1523788721237</v>
+      </c>
+      <c r="AE31" s="21" t="n">
         <f aca="false">+AE29/AE33</f>
-        <v>5.55729152351607</v>
-      </c>
-      <c r="AF31" s="0"/>
+        <v>5.30596508069474</v>
+      </c>
+      <c r="AF31" s="12"/>
     </row>
     <row r="32" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="19"/>
@@ -4118,37 +4106,37 @@
       </c>
       <c r="X32" s="18" t="n">
         <f aca="false">+X31/W31-1</f>
-        <v>-0.264098600658194</v>
+        <v>-0.197670971650766</v>
       </c>
       <c r="Y32" s="18" t="n">
         <f aca="false">+Y31/X31-1</f>
-        <v>-0.0603321905308345</v>
+        <v>-0.146543042976788</v>
       </c>
       <c r="Z32" s="18" t="n">
         <f aca="false">+Z31/Y31-1</f>
-        <v>-0.11774918947879</v>
+        <v>-0.121070979871126</v>
       </c>
       <c r="AA32" s="18" t="n">
         <f aca="false">+AA31/Z31-1</f>
-        <v>-0.35467487809582</v>
+        <v>-0.317371514933479</v>
       </c>
       <c r="AB32" s="18" t="n">
         <f aca="false">+AB31/AA31-1</f>
-        <v>-1.15956144853943</v>
+        <v>-1.02249803197746</v>
       </c>
       <c r="AC32" s="18" t="n">
         <f aca="false">+AC31/AB31-1</f>
-        <v>6.54591504641203</v>
+        <v>41.5410955799374</v>
       </c>
       <c r="AD32" s="18" t="n">
         <f aca="false">+AD31/AC31-1</f>
-        <v>1.04956171947742</v>
+        <v>1.22651531509903</v>
       </c>
       <c r="AE32" s="18" t="n">
         <f aca="false">+AE31/AD31-1</f>
-        <v>0.588585149400397</v>
-      </c>
-      <c r="AF32" s="0"/>
+        <v>0.683162239036393</v>
+      </c>
+      <c r="AF32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
@@ -4304,494 +4292,494 @@
         <f aca="false">+AE33/AD33-1</f>
         <v>-0.01</v>
       </c>
-      <c r="AF34" s="0"/>
-    </row>
-    <row r="36" s="23" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
+      <c r="AF34" s="12"/>
+    </row>
+    <row r="36" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="23" t="n">
+      <c r="B36" s="22" t="n">
         <f aca="false">+B7/B3</f>
         <v>0.776758202688518</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="22" t="n">
         <f aca="false">+C7/C3</f>
         <v>0.905844270259113</v>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="22" t="n">
         <f aca="false">+D7/D3</f>
         <v>0.924114406877319</v>
       </c>
-      <c r="E36" s="23" t="n">
+      <c r="E36" s="22" t="n">
         <f aca="false">+E7/E3</f>
         <v>0.914758609809859</v>
       </c>
-      <c r="F36" s="23" t="n">
+      <c r="F36" s="22" t="n">
         <f aca="false">+F7/F3</f>
         <v>0.888283127703894</v>
       </c>
-      <c r="G36" s="23" t="n">
+      <c r="G36" s="22" t="n">
         <f aca="false">+G7/G3</f>
         <v>0.694047189183472</v>
       </c>
-      <c r="H36" s="23" t="n">
+      <c r="H36" s="22" t="n">
         <f aca="false">+H7/H3</f>
         <v>0.82124328452544</v>
       </c>
-      <c r="I36" s="23" t="n">
+      <c r="I36" s="22" t="n">
         <f aca="false">+I7/I3</f>
         <v>0.794067280672027</v>
       </c>
-      <c r="S36" s="23" t="n">
+      <c r="S36" s="22" t="n">
         <f aca="false">+S7/S3</f>
         <v>0.883160594437198</v>
       </c>
-      <c r="T36" s="23" t="n">
+      <c r="T36" s="22" t="n">
         <f aca="false">+T7/T3</f>
         <v>0.824276275161301</v>
       </c>
-      <c r="U36" s="23" t="n">
+      <c r="U36" s="22" t="n">
         <f aca="false">+U7/U3</f>
         <v>0.83</v>
       </c>
-      <c r="V36" s="23" t="n">
+      <c r="V36" s="22" t="n">
         <f aca="false">+V7/V3</f>
         <v>0.835</v>
       </c>
-      <c r="W36" s="23" t="n">
+      <c r="W36" s="22" t="n">
         <f aca="false">+W7/W3</f>
         <v>0.84</v>
       </c>
-      <c r="X36" s="23" t="n">
+      <c r="X36" s="22" t="n">
         <f aca="false">+X7/X3</f>
         <v>0.845</v>
       </c>
-      <c r="Y36" s="23" t="n">
+      <c r="Y36" s="22" t="n">
         <f aca="false">+Y7/Y3</f>
         <v>0.85</v>
       </c>
-      <c r="Z36" s="23" t="n">
+      <c r="Z36" s="22" t="n">
         <f aca="false">+Z7/Z3</f>
         <v>0.855</v>
       </c>
-      <c r="AA36" s="23" t="n">
+      <c r="AA36" s="22" t="n">
         <f aca="false">+AA7/AA3</f>
         <v>0.86</v>
       </c>
-      <c r="AB36" s="23" t="n">
+      <c r="AB36" s="22" t="n">
         <f aca="false">+AB7/AB3</f>
         <v>0.865</v>
       </c>
-      <c r="AC36" s="23" t="n">
+      <c r="AC36" s="22" t="n">
         <f aca="false">+AC7/AC3</f>
         <v>0.87</v>
       </c>
-      <c r="AD36" s="23" t="n">
+      <c r="AD36" s="22" t="n">
         <f aca="false">+AD7/AD3</f>
         <v>0.875</v>
       </c>
-      <c r="AE36" s="23" t="n">
+      <c r="AE36" s="22" t="n">
         <f aca="false">+AE7/AE3</f>
         <v>0.88</v>
       </c>
-      <c r="AF36" s="0"/>
-      <c r="AI36" s="24" t="s">
+      <c r="AF36" s="12"/>
+      <c r="AI36" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="AJ36" s="25" t="n">
+      <c r="AJ36" s="24" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="37" s="23" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
+    <row r="37" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="22" t="n">
         <f aca="false">+B17/B3</f>
         <v>-5.04682332757706</v>
       </c>
-      <c r="C37" s="23" t="n">
+      <c r="C37" s="22" t="n">
         <f aca="false">+C17/C3</f>
         <v>-0.238301642678427</v>
       </c>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="22" t="n">
         <f aca="false">+D17/D3</f>
         <v>0.238166355527899</v>
       </c>
-      <c r="E37" s="23" t="n">
+      <c r="E37" s="22" t="n">
         <f aca="false">+E17/E3</f>
         <v>0.174185688806699</v>
       </c>
-      <c r="F37" s="23" t="n">
+      <c r="F37" s="22" t="n">
         <f aca="false">+F17/F3</f>
         <v>0.00831597500400577</v>
       </c>
-      <c r="G37" s="23" t="n">
+      <c r="G37" s="22" t="n">
         <f aca="false">+G17/G3</f>
         <v>-4.14621425158568</v>
       </c>
-      <c r="H37" s="23" t="n">
+      <c r="H37" s="22" t="n">
         <f aca="false">+H17/H3</f>
         <v>-0.643572895817971</v>
       </c>
-      <c r="I37" s="23" t="n">
+      <c r="I37" s="22" t="n">
         <f aca="false">+I17/I3</f>
         <v>-0.412063375909837</v>
       </c>
-      <c r="S37" s="23" t="n">
+      <c r="S37" s="22" t="n">
         <f aca="false">+S17/S3</f>
         <v>-1.17145542588827</v>
       </c>
-      <c r="T37" s="23" t="n">
+      <c r="T37" s="22" t="n">
         <f aca="false">+T17/T3</f>
         <v>-1.22226905401463</v>
       </c>
-      <c r="U37" s="23" t="n">
+      <c r="U37" s="22" t="n">
         <f aca="false">+U17/U3</f>
         <v>-0.95901351407669</v>
       </c>
-      <c r="V37" s="23" t="n">
+      <c r="V37" s="22" t="n">
         <f aca="false">+V17/V3</f>
         <v>-0.729539979346503</v>
       </c>
-      <c r="W37" s="23" t="n">
+      <c r="W37" s="22" t="n">
         <f aca="false">+W17/W3</f>
         <v>-0.550702203863558</v>
       </c>
-      <c r="X37" s="23" t="n">
+      <c r="X37" s="22" t="n">
         <f aca="false">+X17/X3</f>
-        <v>-0.36526881104725</v>
-      </c>
-      <c r="Y37" s="23" t="n">
+        <v>-0.411817611472144</v>
+      </c>
+      <c r="Y37" s="22" t="n">
         <f aca="false">+Y17/Y3</f>
-        <v>-0.284244380608655</v>
-      </c>
-      <c r="Z37" s="23" t="n">
+        <v>-0.28075439789909</v>
+      </c>
+      <c r="Z37" s="22" t="n">
         <f aca="false">+Z17/Z3</f>
-        <v>-0.208520681714303</v>
-      </c>
-      <c r="AA37" s="23" t="n">
+        <v>-0.205248310385952</v>
+      </c>
+      <c r="AA37" s="22" t="n">
         <f aca="false">+AA17/AA3</f>
-        <v>-0.114893958238111</v>
-      </c>
-      <c r="AB37" s="23" t="n">
+        <v>-0.120061463381972</v>
+      </c>
+      <c r="AB37" s="22" t="n">
         <f aca="false">+AB17/AB3</f>
-        <v>0.00479944861343101</v>
-      </c>
-      <c r="AC37" s="23" t="n">
+        <v>-0.00708859029751777</v>
+      </c>
+      <c r="AC37" s="22" t="n">
         <f aca="false">+AC17/AC3</f>
-        <v>0.104567305969578</v>
-      </c>
-      <c r="AD37" s="23" t="n">
+        <v>0.0873563933227408</v>
+      </c>
+      <c r="AD37" s="22" t="n">
         <f aca="false">+AD17/AD3</f>
-        <v>0.188073223306032</v>
-      </c>
-      <c r="AE37" s="23" t="n">
+        <v>0.172627532469125</v>
+      </c>
+      <c r="AE37" s="22" t="n">
         <f aca="false">+AE17/AE3</f>
-        <v>0.258212831440805</v>
-      </c>
-      <c r="AF37" s="0"/>
-      <c r="AI37" s="26" t="s">
+        <v>0.249665734267164</v>
+      </c>
+      <c r="AF37" s="12"/>
+      <c r="AI37" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="AJ37" s="27" t="n">
+      <c r="AJ37" s="26" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="38" s="23" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23" t="s">
+    <row r="38" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="23" t="n">
+      <c r="B38" s="22" t="n">
         <f aca="false">+B29/B3</f>
         <v>-4.67191503290105</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C38" s="22" t="n">
         <f aca="false">+C29/C3</f>
         <v>-0.0785243582579453</v>
       </c>
-      <c r="D38" s="23" t="n">
+      <c r="D38" s="22" t="n">
         <f aca="false">+D29/D3</f>
         <v>0.152434948950195</v>
       </c>
-      <c r="E38" s="23" t="n">
+      <c r="E38" s="22" t="n">
         <f aca="false">+E29/E3</f>
         <v>0.0377346088282596</v>
       </c>
-      <c r="F38" s="23" t="n">
+      <c r="F38" s="22" t="n">
         <f aca="false">+F29/F3</f>
         <v>0.00338887998718154</v>
       </c>
-      <c r="G38" s="23" t="n">
+      <c r="G38" s="22" t="n">
         <f aca="false">+G29/G3</f>
         <v>-4.00117808828732</v>
       </c>
-      <c r="H38" s="23" t="n">
+      <c r="H38" s="22" t="n">
         <f aca="false">+H29/H3</f>
         <v>-0.745802828399874</v>
       </c>
-      <c r="I38" s="23" t="n">
+      <c r="I38" s="22" t="n">
         <f aca="false">+I29/I3</f>
         <v>-0.427067619564598</v>
       </c>
-      <c r="S38" s="23" t="n">
+      <c r="S38" s="22" t="n">
         <f aca="false">+S29/S3</f>
         <v>-0.977448929321465</v>
       </c>
-      <c r="T38" s="23" t="n">
+      <c r="T38" s="22" t="n">
         <f aca="false">+T29/T3</f>
         <v>-1.18438834311434</v>
       </c>
-      <c r="U38" s="23" t="n">
+      <c r="U38" s="22" t="n">
         <f aca="false">+U29/U3</f>
         <v>-1.00282107392772</v>
       </c>
-      <c r="V38" s="23" t="n">
+      <c r="V38" s="22" t="n">
         <f aca="false">+V29/V3</f>
         <v>-0.765284126169269</v>
       </c>
-      <c r="W38" s="23" t="n">
+      <c r="W38" s="22" t="n">
         <f aca="false">+W29/W3</f>
         <v>-0.578209571574444</v>
       </c>
-      <c r="X38" s="23" t="n">
+      <c r="X38" s="22" t="n">
         <f aca="false">+X29/X3</f>
-        <v>-0.346707967494745</v>
-      </c>
-      <c r="Y38" s="23" t="n">
+        <v>-0.392542889321466</v>
+      </c>
+      <c r="Y38" s="22" t="n">
         <f aca="false">+Y29/Y3</f>
-        <v>-0.268777010981567</v>
-      </c>
-      <c r="Z38" s="23" t="n">
+        <v>-0.265334620178547</v>
+      </c>
+      <c r="Z38" s="22" t="n">
         <f aca="false">+Z29/Z3</f>
-        <v>-0.195631207025064</v>
-      </c>
-      <c r="AA38" s="23" t="n">
+        <v>-0.192398495618833</v>
+      </c>
+      <c r="AA38" s="22" t="n">
         <f aca="false">+AA29/AA3</f>
-        <v>-0.104152729330412</v>
-      </c>
-      <c r="AB38" s="23" t="n">
+        <v>-0.109263299712124</v>
+      </c>
+      <c r="AB38" s="22" t="n">
         <f aca="false">+AB29/AB3</f>
-        <v>0.0138256913930106</v>
-      </c>
-      <c r="AC38" s="23" t="n">
+        <v>0.00206239586337019</v>
+      </c>
+      <c r="AC38" s="22" t="n">
         <f aca="false">+AC29/AC3</f>
-        <v>0.087528998120739</v>
-      </c>
-      <c r="AD38" s="23" t="n">
+        <v>0.0742386442323298</v>
+      </c>
+      <c r="AD38" s="22" t="n">
         <f aca="false">+AD29/AD3</f>
-        <v>0.151796686370558</v>
-      </c>
-      <c r="AE38" s="23" t="n">
+        <v>0.139863712454629</v>
+      </c>
+      <c r="AE38" s="22" t="n">
         <f aca="false">+AE29/AE3</f>
-        <v>0.205802191447839</v>
-      </c>
-      <c r="AF38" s="0"/>
-      <c r="AI38" s="28" t="s">
+        <v>0.19919588565891</v>
+      </c>
+      <c r="AF38" s="12"/>
+      <c r="AI38" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="AJ38" s="29" t="n">
+      <c r="AJ38" s="28" t="n">
         <f aca="false">+Main!E13</f>
         <v>0.12525</v>
       </c>
     </row>
-    <row r="39" s="23" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="30" t="s">
+    <row r="39" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="23" t="n">
+      <c r="E39" s="22" t="n">
         <f aca="false">+E37+E4</f>
         <v>0.174185688806699</v>
       </c>
-      <c r="F39" s="23" t="n">
+      <c r="F39" s="22" t="n">
         <f aca="false">+F37+F4</f>
         <v>0.417135487639588</v>
       </c>
-      <c r="G39" s="23" t="n">
+      <c r="G39" s="22" t="n">
         <f aca="false">+G37+G4</f>
         <v>-3.76595659825476</v>
       </c>
-      <c r="H39" s="23" t="n">
+      <c r="H39" s="22" t="n">
         <f aca="false">+H37+H4</f>
         <v>-0.243328594266887</v>
       </c>
-      <c r="I39" s="23" t="n">
+      <c r="I39" s="22" t="n">
         <f aca="false">+I37+I4</f>
         <v>0.0491130534347264</v>
       </c>
-      <c r="S39" s="23" t="n">
+      <c r="S39" s="22" t="n">
         <f aca="false">+S37+S4</f>
         <v>-0.68789517125048</v>
       </c>
-      <c r="T39" s="23" t="n">
+      <c r="T39" s="22" t="n">
         <f aca="false">+T37+T4</f>
         <v>-0.812692959671558</v>
       </c>
-      <c r="U39" s="23" t="n">
+      <c r="U39" s="22" t="n">
         <f aca="false">+U37+U4</f>
         <v>-0.55901351407669</v>
       </c>
-      <c r="V39" s="23" t="n">
+      <c r="V39" s="22" t="n">
         <f aca="false">+V37+V4</f>
         <v>-0.329539979346503</v>
       </c>
-      <c r="W39" s="23" t="n">
+      <c r="W39" s="22" t="n">
         <f aca="false">+W37+W4</f>
         <v>-0.200702203863558</v>
       </c>
-      <c r="X39" s="23" t="n">
+      <c r="X39" s="22" t="n">
         <f aca="false">+X37+X4</f>
-        <v>-0.0152688110472499</v>
-      </c>
-      <c r="Y39" s="23" t="n">
+        <v>-0.111817611472144</v>
+      </c>
+      <c r="Y39" s="22" t="n">
         <f aca="false">+Y37+Y4</f>
-        <v>-0.0842443806086548</v>
-      </c>
-      <c r="Z39" s="23" t="n">
+        <v>-0.0307543978990901</v>
+      </c>
+      <c r="Z39" s="22" t="n">
         <f aca="false">+Z37+Z4</f>
-        <v>-0.00852068171430326</v>
-      </c>
-      <c r="AA39" s="23" t="n">
+        <v>-0.00524831038595192</v>
+      </c>
+      <c r="AA39" s="22" t="n">
         <f aca="false">+AA37+AA4</f>
-        <v>0.0851060417618887</v>
-      </c>
-      <c r="AB39" s="23" t="n">
+        <v>0.0699385366180277</v>
+      </c>
+      <c r="AB39" s="22" t="n">
         <f aca="false">+AB37+AB4</f>
-        <v>0.194799448613431</v>
-      </c>
-      <c r="AC39" s="23" t="n">
+        <v>0.172911409702482</v>
+      </c>
+      <c r="AC39" s="22" t="n">
         <f aca="false">+AC37+AC4</f>
-        <v>0.284567305969578</v>
-      </c>
-      <c r="AD39" s="23" t="n">
+        <v>0.257356393322741</v>
+      </c>
+      <c r="AD39" s="22" t="n">
         <f aca="false">+AD37+AD4</f>
-        <v>0.358073223306032</v>
-      </c>
-      <c r="AE39" s="23" t="n">
+        <v>0.342627532469125</v>
+      </c>
+      <c r="AE39" s="22" t="n">
         <f aca="false">+AE37+AE4</f>
-        <v>0.418212831440805</v>
-      </c>
-      <c r="AF39" s="0"/>
-      <c r="AI39" s="26" t="s">
+        <v>0.419665734267164</v>
+      </c>
+      <c r="AF39" s="12"/>
+      <c r="AI39" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="AJ39" s="31" t="n">
+      <c r="AJ39" s="30" t="n">
         <f aca="false">+NPV(AJ38,U29:CW29)</f>
-        <v>1617314.0626308</v>
-      </c>
-    </row>
-    <row r="40" s="23" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23" t="s">
+        <v>1104189.45423431</v>
+      </c>
+    </row>
+    <row r="40" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B40" s="23" t="n">
+      <c r="B40" s="22" t="n">
         <f aca="false">+B23/B21</f>
         <v>0.0636703357356461</v>
       </c>
-      <c r="C40" s="23" t="n">
+      <c r="C40" s="22" t="n">
         <f aca="false">+C23/C21</f>
         <v>0.469924556514647</v>
       </c>
-      <c r="D40" s="23" t="n">
+      <c r="D40" s="22" t="n">
         <f aca="false">+D23/D21</f>
         <v>-0.0772051940042072</v>
       </c>
-      <c r="E40" s="23" t="n">
+      <c r="E40" s="22" t="n">
         <f aca="false">+E23/E21</f>
         <v>0.0455309104055462</v>
       </c>
-      <c r="F40" s="23" t="n">
+      <c r="F40" s="22" t="n">
         <f aca="false">+F23/F21</f>
         <v>0.277231525579966</v>
       </c>
-      <c r="G40" s="23" t="n">
+      <c r="G40" s="22" t="n">
         <f aca="false">+G23/G21</f>
         <v>0.00944490846294499</v>
       </c>
-      <c r="H40" s="23" t="n">
+      <c r="H40" s="22" t="n">
         <f aca="false">+H23/H21</f>
         <v>-0.109246783259239</v>
       </c>
-      <c r="I40" s="23" t="n">
+      <c r="I40" s="22" t="n">
         <f aca="false">+I23/I21</f>
         <v>-0.0047839800173578</v>
       </c>
-      <c r="R40" s="23" t="n">
+      <c r="R40" s="22" t="n">
         <f aca="false">+R23/R21</f>
         <v>0.21997443755755</v>
       </c>
-      <c r="S40" s="23" t="n">
+      <c r="S40" s="22" t="n">
         <f aca="false">+S23/S21</f>
         <v>0.0768544052171874</v>
       </c>
-      <c r="T40" s="23" t="n">
+      <c r="T40" s="22" t="n">
         <f aca="false">+T23/T21</f>
         <v>-0.0202514274151832</v>
       </c>
-      <c r="U40" s="23" t="n">
+      <c r="U40" s="22" t="n">
         <f aca="false">+U23/U21</f>
         <v>-0.1</v>
       </c>
-      <c r="V40" s="23" t="n">
+      <c r="V40" s="22" t="n">
         <f aca="false">+V23/V21</f>
         <v>-0.1</v>
       </c>
-      <c r="W40" s="23" t="n">
+      <c r="W40" s="22" t="n">
         <f aca="false">+W23/W21</f>
         <v>-0.1</v>
       </c>
-      <c r="X40" s="23" t="n">
+      <c r="X40" s="22" t="n">
         <f aca="false">+X23/X21</f>
         <v>-0</v>
       </c>
-      <c r="Y40" s="23" t="n">
+      <c r="Y40" s="22" t="n">
         <f aca="false">+Y23/Y21</f>
         <v>-0</v>
       </c>
-      <c r="Z40" s="23" t="n">
+      <c r="Z40" s="22" t="n">
         <f aca="false">+Z23/Z21</f>
         <v>-0</v>
       </c>
-      <c r="AA40" s="23" t="n">
+      <c r="AA40" s="22" t="n">
         <f aca="false">+AA23/AA21</f>
         <v>-0</v>
       </c>
-      <c r="AB40" s="23" t="n">
+      <c r="AB40" s="22" t="n">
         <f aca="false">+AB23/AB21</f>
         <v>0</v>
       </c>
-      <c r="AC40" s="23" t="n">
+      <c r="AC40" s="22" t="n">
         <f aca="false">+AC23/AC21</f>
         <v>0.22</v>
       </c>
-      <c r="AD40" s="23" t="n">
+      <c r="AD40" s="22" t="n">
         <f aca="false">+AD23/AD21</f>
         <v>0.22</v>
       </c>
-      <c r="AE40" s="23" t="n">
+      <c r="AE40" s="22" t="n">
         <f aca="false">+AE23/AE21</f>
         <v>0.22</v>
       </c>
-      <c r="AF40" s="32"/>
-      <c r="AI40" s="28" t="s">
+      <c r="AF40" s="1"/>
+      <c r="AI40" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AJ40" s="33" t="n">
-        <f aca="false">+AJ39/(Main!F2+Main!F3)-1</f>
-        <v>3059.91175361555</v>
-      </c>
-    </row>
-    <row r="41" s="23" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AF41" s="32"/>
-      <c r="AI41" s="34" t="s">
+      <c r="AJ40" s="31" t="n">
+        <f aca="false">+(AJ39/100)/(Main!F2+Main!F3)-1</f>
+        <v>19.8977746300329</v>
+      </c>
+    </row>
+    <row r="41" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF41" s="1"/>
+      <c r="AI41" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="AJ41" s="35" t="n">
+      <c r="AJ41" s="33" t="n">
         <f aca="false">+AJ40/Main!F1-1</f>
-        <v>127.029780486006</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>-0.167457128450507</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>63</v>
       </c>
@@ -4837,39 +4825,38 @@
       </c>
       <c r="X42" s="3" t="n">
         <f aca="false">+SUM(X51,X52)-SUM(X62,X63)</f>
-        <v>412264.147039069</v>
+        <v>388365.344333918</v>
       </c>
       <c r="Y42" s="3" t="n">
         <f aca="false">+SUM(Y51,Y52)-SUM(Y62,Y63)</f>
-        <v>371159.070806137</v>
+        <v>373512.595812329</v>
       </c>
       <c r="Z42" s="3" t="n">
         <f aca="false">+SUM(Z51,Z52)-SUM(Z62,Z63)</f>
-        <v>326625.375410475</v>
+        <v>329445.242786186</v>
       </c>
       <c r="AA42" s="3" t="n">
         <f aca="false">+SUM(AA51,AA52)-SUM(AA62,AA63)</f>
-        <v>332060.269023595</v>
+        <v>326368.50414862</v>
       </c>
       <c r="AB42" s="3" t="n">
         <f aca="false">+SUM(AB51,AB52)-SUM(AB62,AB63)</f>
-        <v>463589.144107789</v>
+        <v>446062.01378226</v>
       </c>
       <c r="AC42" s="3" t="n">
         <f aca="false">+SUM(AC51,AC52)-SUM(AC62,AC63)</f>
-        <v>589116.604944617</v>
+        <v>556273.241151833</v>
       </c>
       <c r="AD42" s="3" t="n">
         <f aca="false">+SUM(AD51,AD52)-SUM(AD62,AD63)</f>
-        <v>754187.228669082</v>
+        <v>715725.014259322</v>
       </c>
       <c r="AE42" s="3" t="n">
         <f aca="false">+SUM(AE51,AE52)-SUM(AE62,AE63)</f>
-        <v>936418.553623021</v>
-      </c>
-      <c r="AF42" s="36"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>908882.572026028</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>64</v>
       </c>
@@ -4931,39 +4918,38 @@
       </c>
       <c r="X43" s="3" t="n">
         <f aca="false">+X17*(1-X40)</f>
-        <v>-1377567.603594</v>
+        <v>-1495597.839372</v>
       </c>
       <c r="Y43" s="3" t="n">
         <f aca="false">+Y17*(1-Y40)</f>
-        <v>-1286392.393944</v>
+        <v>-1274519.52999</v>
       </c>
       <c r="Z43" s="3" t="n">
         <f aca="false">+Z17*(1-Z40)</f>
-        <v>-1132431.54371424</v>
+        <v>-1118100.298518</v>
       </c>
       <c r="AA43" s="3" t="n">
         <f aca="false">+AA17*(1-AA40)</f>
-        <v>-748757.627807615</v>
+        <v>-778308.487785361</v>
       </c>
       <c r="AB43" s="3" t="n">
         <f aca="false">+AB17*(1-AB40)</f>
-        <v>37220.5147971679</v>
+        <v>-54223.8084619828</v>
       </c>
       <c r="AC43" s="3" t="n">
         <f aca="false">+AC17*(1-AC40)</f>
-        <v>746386.126933072</v>
+        <v>609825.107385129</v>
       </c>
       <c r="AD43" s="3" t="n">
         <f aca="false">+AD17*(1-AD40)</f>
-        <v>1570653.79855856</v>
+        <v>1409959.15055601</v>
       </c>
       <c r="AE43" s="3" t="n">
         <f aca="false">+AE17*(1-AE40)</f>
-        <v>2501435.50791274</v>
-      </c>
-      <c r="AF43" s="36"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2385839.75246059</v>
+      </c>
+    </row>
+    <row r="44" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>65</v>
       </c>
@@ -4989,43 +4975,42 @@
       </c>
       <c r="X44" s="3" t="n">
         <f aca="false">+X43+X88-X106-(X42-W42)</f>
-        <v>-1417929.56352293</v>
+        <v>-1512060.99659578</v>
       </c>
       <c r="Y44" s="3" t="n">
         <f aca="false">+Y43+Y88-Y106-(Y42-X42)</f>
-        <v>-1185319.94171107</v>
+        <v>-1199699.40546841</v>
       </c>
       <c r="Z44" s="3" t="n">
         <f aca="false">+Z43+Z88-Z106-(Z42-Y42)</f>
-        <v>-1003943.52191858</v>
+        <v>-990078.619091858</v>
       </c>
       <c r="AA44" s="3" t="n">
         <f aca="false">+AA43+AA88-AA106-(AA42-Z42)</f>
-        <v>-636656.464460736</v>
+        <v>-657695.692187795</v>
       </c>
       <c r="AB44" s="3" t="n">
         <f aca="false">+AB43+AB88-AB106-(AB42-AA42)</f>
-        <v>70242.1194569743</v>
+        <v>-9366.83835162236</v>
       </c>
       <c r="AC44" s="3" t="n">
         <f aca="false">+AC43+AC88-AC106-(AC42-AB42)</f>
-        <v>851229.337737843</v>
+        <v>729984.551657156</v>
       </c>
       <c r="AD44" s="3" t="n">
         <f aca="false">+AD43+AD88-AD106-(AD42-AC42)</f>
-        <v>1728102.11513233</v>
+        <v>1573026.31774676</v>
       </c>
       <c r="AE44" s="3" t="n">
         <f aca="false">+AE43+AE88-AE106-(AE42-AD42)</f>
-        <v>2770730.69937634</v>
-      </c>
-      <c r="AF44" s="36"/>
-    </row>
-    <row r="45" s="23" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AF45" s="32"/>
+        <v>2644208.71111142</v>
+      </c>
+    </row>
+    <row r="45" s="22" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AF45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AF46" s="32"/>
+      <c r="AF46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
@@ -5059,10 +5044,10 @@
         <f aca="false">+403469+9799</f>
         <v>413268</v>
       </c>
-      <c r="AI47" s="37" t="s">
+      <c r="AI47" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="AJ47" s="38" t="n">
+      <c r="AJ47" s="35" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5091,10 +5076,10 @@
       <c r="T48" s="3" t="n">
         <v>15575</v>
       </c>
-      <c r="AI48" s="39" t="s">
+      <c r="AI48" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="AJ48" s="40" t="n">
+      <c r="AJ48" s="37" t="n">
         <f aca="false">+Main!E13</f>
         <v>0.12525</v>
       </c>
@@ -5124,49 +5109,49 @@
       <c r="T49" s="3" t="n">
         <v>1252474</v>
       </c>
-      <c r="AI49" s="41" t="s">
+      <c r="AI49" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="AJ49" s="42" t="n">
+      <c r="AJ49" s="39" t="n">
         <f aca="false">+NPV(AJ48,U44:AD44,AE44+AJ50)/1000</f>
-        <v>2045.68376926599</v>
-      </c>
-    </row>
-    <row r="50" s="44" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="43" t="s">
+        <v>1518.76344594274</v>
+      </c>
+    </row>
+    <row r="50" s="41" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="44" t="n">
+      <c r="D50" s="41" t="n">
         <v>78791</v>
       </c>
-      <c r="F50" s="44" t="n">
+      <c r="F50" s="41" t="n">
         <v>90793</v>
       </c>
-      <c r="G50" s="44" t="n">
+      <c r="G50" s="41" t="n">
         <v>96422</v>
       </c>
-      <c r="H50" s="44" t="n">
+      <c r="H50" s="41" t="n">
         <v>73689</v>
       </c>
-      <c r="I50" s="44" t="n">
+      <c r="I50" s="41" t="n">
         <v>57019</v>
       </c>
-      <c r="R50" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="44" t="n">
+      <c r="R50" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="41" t="n">
         <v>78791</v>
       </c>
-      <c r="T50" s="44" t="n">
+      <c r="T50" s="41" t="n">
         <v>73689</v>
       </c>
-      <c r="AF50" s="0"/>
-      <c r="AI50" s="39" t="s">
+      <c r="AF50" s="12"/>
+      <c r="AI50" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="AJ50" s="45" t="n">
+      <c r="AJ50" s="42" t="n">
         <f aca="false">+AE44*(1+AJ47)/(AJ48-AJ47)</f>
-        <v>24281457.7559228</v>
+        <v>23172675.0388072</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5208,42 +5193,42 @@
       </c>
       <c r="X51" s="3" t="n">
         <f aca="false">+(X111/365)*X3</f>
-        <v>661283.123690959</v>
+        <v>636791.156146849</v>
       </c>
       <c r="Y51" s="3" t="n">
         <f aca="false">+(Y111/365)*Y3</f>
-        <v>781140.689859945</v>
+        <v>783551.617915069</v>
       </c>
       <c r="Z51" s="3" t="n">
         <f aca="false">+(Z111/365)*Z3</f>
-        <v>937368.827831934</v>
+        <v>940261.941498082</v>
       </c>
       <c r="AA51" s="3" t="n">
         <f aca="false">+(AA111/365)*AA3</f>
-        <v>1106987.94905867</v>
+        <v>1101151.20704331</v>
       </c>
       <c r="AB51" s="3" t="n">
         <f aca="false">+(AB111/365)*AB3</f>
-        <v>1317315.65937981</v>
+        <v>1299358.42431111</v>
       </c>
       <c r="AC51" s="3" t="n">
         <f aca="false">+(AC111/365)*AC3</f>
-        <v>1529360.98648643</v>
+        <v>1495729.20553361</v>
       </c>
       <c r="AD51" s="3" t="n">
         <f aca="false">+(AD111/365)*AD3</f>
-        <v>1789352.35418913</v>
+        <v>1750003.17047432</v>
       </c>
       <c r="AE51" s="3" t="n">
         <f aca="false">+(AE111/365)*AE3</f>
-        <v>2075648.73085939</v>
-      </c>
-      <c r="AI51" s="46" t="s">
+        <v>2047503.70945495</v>
+      </c>
+      <c r="AI51" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="AJ51" s="47" t="n">
+      <c r="AJ51" s="44" t="n">
         <f aca="false">+AJ49/(Main!F7)-1</f>
-        <v>-0.813438537226989</v>
+        <v>-0.861492409365441</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5271,47 +5256,47 @@
       <c r="T52" s="3" t="n">
         <v>85267</v>
       </c>
-      <c r="U52" s="48" t="n">
+      <c r="U52" s="45" t="n">
         <f aca="false">+T52*1.5</f>
         <v>127900.5</v>
       </c>
-      <c r="V52" s="48" t="n">
+      <c r="V52" s="45" t="n">
         <f aca="false">+U52*1.4</f>
         <v>179060.7</v>
       </c>
-      <c r="W52" s="48" t="n">
+      <c r="W52" s="45" t="n">
         <f aca="false">+V52*1.4</f>
         <v>250684.98</v>
       </c>
-      <c r="X52" s="48" t="n">
+      <c r="X52" s="45" t="n">
         <f aca="false">+W52*1.3</f>
         <v>325890.474</v>
       </c>
-      <c r="Y52" s="48" t="n">
+      <c r="Y52" s="45" t="n">
         <f aca="false">+X52*1.2</f>
         <v>391068.5688</v>
       </c>
-      <c r="Z52" s="48" t="n">
+      <c r="Z52" s="45" t="n">
         <f aca="false">+Y52*1.1</f>
         <v>430175.42568</v>
       </c>
-      <c r="AA52" s="48" t="n">
+      <c r="AA52" s="45" t="n">
         <f aca="false">+Z52*1.1</f>
         <v>473192.968248</v>
       </c>
-      <c r="AB52" s="48" t="n">
+      <c r="AB52" s="45" t="n">
         <f aca="false">+AA52*1.1</f>
         <v>520512.2650728</v>
       </c>
-      <c r="AC52" s="48" t="n">
+      <c r="AC52" s="45" t="n">
         <f aca="false">+AB52*1.1</f>
         <v>572563.49158008</v>
       </c>
-      <c r="AD52" s="48" t="n">
+      <c r="AD52" s="45" t="n">
         <f aca="false">+AC52*1.1</f>
         <v>629819.840738088</v>
       </c>
-      <c r="AE52" s="48" t="n">
+      <c r="AE52" s="45" t="n">
         <f aca="false">+AD52*1.1</f>
         <v>692801.824811897</v>
       </c>
@@ -5628,35 +5613,35 @@
       </c>
       <c r="X62" s="3" t="n">
         <f aca="false">+(X112/365)*X5</f>
-        <v>16015.4506518904</v>
+        <v>15422.2858129315</v>
       </c>
       <c r="Y62" s="3" t="n">
         <f aca="false">+(Y112/365)*Y5</f>
-        <v>18598.5878538082</v>
+        <v>18655.9909027397</v>
       </c>
       <c r="Z62" s="3" t="n">
         <f aca="false">+(Z112/365)*Z5</f>
-        <v>23731.7981014593</v>
+        <v>23805.0443918959</v>
       </c>
       <c r="AA62" s="3" t="n">
         <f aca="false">+(AA112/365)*AA5</f>
-        <v>27496.1522830701</v>
+        <v>27351.1751426887</v>
       </c>
       <c r="AB62" s="3" t="n">
         <f aca="false">+(AB112/365)*AB5</f>
-        <v>31551.8347448229</v>
+        <v>31121.730001645</v>
       </c>
       <c r="AC62" s="3" t="n">
         <f aca="false">+(AC112/365)*AC5</f>
-        <v>35852.2329618951</v>
+        <v>35063.8158018534</v>
       </c>
       <c r="AD62" s="3" t="n">
         <f aca="false">+(AD112/365)*AD5</f>
-        <v>40333.762082132</v>
+        <v>39446.7927770851</v>
       </c>
       <c r="AE62" s="3" t="n">
         <f aca="false">+(AE112/365)*AE5</f>
-        <v>44915.6774546621</v>
+        <v>44306.6376472219</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5684,47 +5669,47 @@
       <c r="T63" s="3" t="n">
         <v>66535</v>
       </c>
-      <c r="U63" s="48" t="n">
+      <c r="U63" s="45" t="n">
         <f aca="false">+T63*2</f>
         <v>133070</v>
       </c>
-      <c r="V63" s="48" t="n">
+      <c r="V63" s="45" t="n">
         <f aca="false">+U63*2</f>
         <v>266140</v>
       </c>
-      <c r="W63" s="48" t="n">
+      <c r="W63" s="45" t="n">
         <f aca="false">+V63*1.5</f>
         <v>399210</v>
       </c>
-      <c r="X63" s="48" t="n">
+      <c r="X63" s="45" t="n">
         <f aca="false">+W63*1.4</f>
         <v>558894</v>
       </c>
-      <c r="Y63" s="48" t="n">
+      <c r="Y63" s="45" t="n">
         <f aca="false">+X63*1.4</f>
         <v>782451.6</v>
       </c>
-      <c r="Z63" s="48" t="n">
+      <c r="Z63" s="45" t="n">
         <f aca="false">+Y63*1.3</f>
         <v>1017187.08</v>
       </c>
-      <c r="AA63" s="48" t="n">
+      <c r="AA63" s="45" t="n">
         <f aca="false">+Z63*1.2</f>
         <v>1220624.496</v>
       </c>
-      <c r="AB63" s="48" t="n">
+      <c r="AB63" s="45" t="n">
         <f aca="false">+AA63*1.1</f>
         <v>1342686.9456</v>
       </c>
-      <c r="AC63" s="48" t="n">
+      <c r="AC63" s="45" t="n">
         <f aca="false">+AB63*1.1</f>
         <v>1476955.64016</v>
       </c>
-      <c r="AD63" s="48" t="n">
+      <c r="AD63" s="45" t="n">
         <f aca="false">+AC63*1.1</f>
         <v>1624651.204176</v>
       </c>
-      <c r="AE63" s="48" t="n">
+      <c r="AE63" s="45" t="n">
         <f aca="false">+AD63*1.1</f>
         <v>1787116.3245936</v>
       </c>
@@ -6407,35 +6392,35 @@
       </c>
       <c r="X86" s="3" t="n">
         <f aca="false">+X25</f>
-        <v>-1307567.603594</v>
+        <v>-1425597.839372</v>
       </c>
       <c r="Y86" s="3" t="n">
         <f aca="false">+Y25</f>
-        <v>-1216392.393944</v>
+        <v>-1204519.52999</v>
       </c>
       <c r="Z86" s="3" t="n">
         <f aca="false">+Z25</f>
-        <v>-1062431.54371424</v>
+        <v>-1048100.298518</v>
       </c>
       <c r="AA86" s="3" t="n">
         <f aca="false">+AA25</f>
-        <v>-678757.627807615</v>
+        <v>-708308.487785361</v>
       </c>
       <c r="AB86" s="3" t="n">
         <f aca="false">+AB25</f>
-        <v>107220.514797168</v>
+        <v>15776.1915380172</v>
       </c>
       <c r="AC86" s="3" t="n">
         <f aca="false">+AC25</f>
-        <v>800986.126933072</v>
+        <v>664425.107385129</v>
       </c>
       <c r="AD86" s="3" t="n">
         <f aca="false">+AD25</f>
-        <v>1625253.79855856</v>
+        <v>1464559.15055601</v>
       </c>
       <c r="AE86" s="3" t="n">
         <f aca="false">+AE25</f>
-        <v>2556035.50791274</v>
+        <v>2440439.75246059</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7347,69 +7332,69 @@
         <f aca="false">+AE106/AD106-1</f>
         <v>0.4</v>
       </c>
-      <c r="AF107" s="0"/>
-    </row>
-    <row r="108" s="16" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="15" t="s">
+      <c r="AF107" s="12"/>
+    </row>
+    <row r="108" s="17" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B108" s="16" t="n">
+      <c r="B108" s="17" t="n">
         <f aca="false">+B104-B106</f>
         <v>-178642</v>
       </c>
-      <c r="C108" s="16" t="n">
+      <c r="C108" s="17" t="n">
         <f aca="false">+C104-C106</f>
         <v>61161</v>
       </c>
-      <c r="D108" s="16" t="n">
+      <c r="D108" s="17" t="n">
         <f aca="false">+D104-D106</f>
         <v>72429</v>
       </c>
-      <c r="E108" s="16" t="n">
+      <c r="E108" s="17" t="n">
         <f aca="false">+E104-E106</f>
         <v>96303</v>
       </c>
-      <c r="F108" s="16" t="n">
+      <c r="F108" s="17" t="n">
         <f aca="false">+F104-F106</f>
         <v>61321</v>
       </c>
-      <c r="G108" s="16" t="n">
+      <c r="G108" s="17" t="n">
         <f aca="false">+G104-G106</f>
         <v>49461</v>
       </c>
-      <c r="H108" s="16" t="n">
+      <c r="H108" s="17" t="n">
         <f aca="false">+H104-H106</f>
         <v>39152</v>
       </c>
-      <c r="I108" s="16" t="n">
+      <c r="I108" s="17" t="n">
         <f aca="false">+I104-I106</f>
         <v>89496</v>
       </c>
-      <c r="J108" s="16" t="n">
+      <c r="J108" s="17" t="n">
         <f aca="false">+J104-J106</f>
         <v>0</v>
       </c>
-      <c r="K108" s="16" t="n">
+      <c r="K108" s="17" t="n">
         <f aca="false">+K104-K106</f>
         <v>0</v>
       </c>
-      <c r="L108" s="16" t="n">
+      <c r="L108" s="17" t="n">
         <f aca="false">+L104-L106</f>
         <v>0</v>
       </c>
-      <c r="R108" s="16" t="n">
+      <c r="R108" s="17" t="n">
         <f aca="false">+R104-R106</f>
         <v>1043597</v>
       </c>
-      <c r="S108" s="16" t="n">
+      <c r="S108" s="17" t="n">
         <f aca="false">+S104-S106</f>
         <v>-63694</v>
       </c>
-      <c r="T108" s="16" t="n">
+      <c r="T108" s="17" t="n">
         <f aca="false">+T104-T106</f>
         <v>246237</v>
       </c>
-      <c r="AF108" s="0"/>
+      <c r="AF108" s="12"/>
     </row>
     <row r="109" s="18" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="19"/>
@@ -7438,7 +7423,7 @@
         <f aca="false">+T108/S108-1</f>
         <v>-4.86593713693598</v>
       </c>
-      <c r="AF109" s="0"/>
+      <c r="AF109" s="12"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
